--- a/Result/profitability/2328.xlsx
+++ b/Result/profitability/2328.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.49</v>
       </c>
       <c r="M2" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="N2" t="n">
-        <v>12.0975</v>
+        <v>11.26375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0.34125</v>
+        <v>0.2575</v>
       </c>
       <c r="N3" t="n">
-        <v>11.32</v>
+        <v>10.875</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.49</v>
       </c>
       <c r="M4" t="n">
-        <v>0.32875</v>
+        <v>0.26625</v>
       </c>
       <c r="N4" t="n">
-        <v>10.60125</v>
+        <v>10.2675</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3075</v>
+        <v>0.23875</v>
       </c>
       <c r="N5" t="n">
-        <v>10.2875</v>
+        <v>9.805</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>0.27625</v>
+        <v>0.225</v>
       </c>
       <c r="N6" t="n">
-        <v>10.27375</v>
+        <v>9.737500000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2625</v>
+        <v>0.21</v>
       </c>
       <c r="N7" t="n">
-        <v>9.76375</v>
+        <v>9.272499999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0.27125</v>
+        <v>0.28125</v>
       </c>
       <c r="N8" t="n">
-        <v>9.42</v>
+        <v>9.515000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.34875</v>
       </c>
       <c r="N9" t="n">
-        <v>9.442500000000001</v>
+        <v>9.442499999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.3125</v>
       </c>
       <c r="N10" t="n">
-        <v>9.282499999999999</v>
+        <v>9.282500000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2328</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5381</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4921</v>
+      </c>
+      <c r="E75" t="n">
+        <v>460</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>17</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-42</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.5775</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.7600000000000007</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09756097560975618</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.5499999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.170212765957447</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.859999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3110394842868653</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
